--- a/02 Data Manipulation/amzn.xlsx
+++ b/02 Data Manipulation/amzn.xlsx
@@ -8,25 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iese365-my.sharepoint.com/personal/dgomezd_iese_edu/Documents/Python-Bootcamp/02 Data Manipulation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_F25DC773A252ABDACC10483009195AEA5BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3145D09C-99EF-4D45-8600-68BCCDA9A558}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_F25DC773A252ABDACC10483009195AEA5BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D80EAA98-2E3A-46A1-B8FF-3D6A07768896}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19365" yWindow="2640" windowWidth="7860" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023" sheetId="1" r:id="rId1"/>
     <sheet name="2024" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
   <si>
     <t>total_revenue</t>
   </si>
@@ -37,13 +48,7 @@
     <t>gross_profit</t>
   </si>
   <si>
-    <t>operating_income</t>
-  </si>
-  <si>
-    <t>pretax_income</t>
-  </si>
-  <si>
-    <t>net_income</t>
+    <t>ebitda</t>
   </si>
 </sst>
 </file>
@@ -394,31 +399,22 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>574.79</v>
       </c>
       <c r="B2">
-        <v>326.29000000000002</v>
+        <v>304.74</v>
       </c>
       <c r="C2">
-        <v>270.05</v>
+        <f>A2-B2</f>
+        <v>270.04999999999995</v>
       </c>
       <c r="D2">
-        <v>68.59</v>
-      </c>
-      <c r="E2">
-        <v>68.61</v>
-      </c>
-      <c r="F2">
-        <v>59.25</v>
+        <v>89.4</v>
       </c>
     </row>
   </sheetData>
@@ -428,18 +424,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{220F588E-0043-43BB-A82E-54A393408607}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -452,31 +446,20 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>691.3</v>
+        <v>637.96</v>
       </c>
       <c r="B2">
-        <v>345.3</v>
+        <v>326.29000000000002</v>
       </c>
       <c r="C2">
-        <v>345.98</v>
+        <f>A2-B2</f>
+        <v>311.67</v>
       </c>
       <c r="D2">
-        <v>76.2</v>
-      </c>
-      <c r="E2">
-        <v>93.06</v>
-      </c>
-      <c r="F2">
-        <v>76.48</v>
+        <v>123.82</v>
       </c>
     </row>
   </sheetData>
